--- a/recruiters.xlsx
+++ b/recruiters.xlsx
@@ -1,15 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Tracker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATS Reference" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DevOps Keywords" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1738,188 +1736,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ATS Platform</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Typical Career URL Pattern</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>company.wd5.myworkdayjobs.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>boards.greenhouse.io</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Lever</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>jobs.lever.co</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Taleo</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>oraclecloud.com/hcmUI</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SAP SuccessFactors</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>jobs.sap.com</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Search Keywords</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Platform Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DevSecOps Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Kubernetes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Terraform</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AWS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Azure</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Python Automation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/recruiters.xlsx
+++ b/recruiters.xlsx
@@ -479,19 +479,51 @@
           <t>Accenture</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Accenture+careers</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -500,19 +532,51 @@
           <t>IBM</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=IBM+careers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -521,19 +585,51 @@
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Capgemini+careers</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -542,19 +638,51 @@
           <t>Cognizant</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Cognizant+careers</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -563,19 +691,51 @@
           <t>TCS</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=TCS+careers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -584,19 +744,51 @@
           <t>Infosys</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Infosys+careers</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -605,19 +797,51 @@
           <t>Wipro</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Wipro+careers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -626,19 +850,51 @@
           <t>HCLTech</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=HCLTech+careers</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -647,19 +903,51 @@
           <t>Tech Mahindra</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Tech Mahindra+careers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -668,19 +956,51 @@
           <t>LTIMindtree</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=LTIMindtree+careers</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -689,19 +1009,51 @@
           <t>Barclays</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Barclays+careers</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -710,19 +1062,51 @@
           <t>Deutsche Bank</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Deutsche Bank+careers</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -731,19 +1115,51 @@
           <t>UBS</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=UBS+careers</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -752,19 +1168,51 @@
           <t>Citi</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Citi+careers</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -773,19 +1221,51 @@
           <t>Mastercard</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Mastercard+careers</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -794,19 +1274,51 @@
           <t>Visa</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Visa+careers</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -815,19 +1327,51 @@
           <t>HSBC</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=HSBC+careers</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -836,19 +1380,51 @@
           <t>Credit Suisse</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Credit Suisse+careers</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -857,19 +1433,51 @@
           <t>Goldman Sachs</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Goldman Sachs+careers</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -878,19 +1486,51 @@
           <t>Morgan Stanley</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Morgan Stanley+careers</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -899,19 +1539,51 @@
           <t>Northern Trust</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Northern Trust+careers</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -920,19 +1592,51 @@
           <t>BNY Mellon</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=BNY Mellon+careers</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -941,19 +1645,51 @@
           <t>State Street</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=State Street+careers</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -962,19 +1698,51 @@
           <t>Honeywell</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Honeywell+careers</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -983,19 +1751,51 @@
           <t>Siemens</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Siemens+careers</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1004,19 +1804,51 @@
           <t>Bosch</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Bosch+careers</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1025,19 +1857,51 @@
           <t>Philips</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Philips+careers</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1046,19 +1910,51 @@
           <t>GE Healthcare</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=GE Healthcare+careers</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1067,19 +1963,51 @@
           <t>John Deere</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=John Deere+careers</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1088,19 +2016,51 @@
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Schneider Electric+careers</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1109,19 +2069,51 @@
           <t>Eaton</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Eaton+careers</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1130,19 +2122,51 @@
           <t>Emerson</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Emerson+careers</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1151,19 +2175,51 @@
           <t>Rockwell Automation</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Rockwell Automation+careers</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1172,19 +2228,51 @@
           <t>Dell Technologies</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Dell Technologies+careers</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1193,19 +2281,51 @@
           <t>HP</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=HP+careers</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1214,19 +2334,51 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Microsoft+careers</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1235,19 +2387,51 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Google+careers</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1256,19 +2440,51 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Amazon+careers</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1277,19 +2493,51 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Oracle+careers</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1298,19 +2546,51 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=SAP+careers</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1319,19 +2599,51 @@
           <t>Salesforce</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Salesforce+careers</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1340,19 +2652,51 @@
           <t>VMware</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=VMware+careers</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1361,19 +2705,51 @@
           <t>Red Hat</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Red Hat+careers</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -1382,19 +2758,51 @@
           <t>ServiceNow</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=ServiceNow+careers</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1403,19 +2811,51 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Snowflake+careers</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1424,19 +2864,51 @@
           <t>Nvidia</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Nvidia+careers</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1445,19 +2917,51 @@
           <t>Intel</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Intel+careers</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1466,19 +2970,51 @@
           <t>AMD</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=AMD+careers</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1487,19 +3023,51 @@
           <t>Cisco</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Cisco+careers</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -1508,19 +3076,51 @@
           <t>Juniper Networks</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Juniper Networks+careers</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -1529,19 +3129,51 @@
           <t>NetApp</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=NetApp+careers</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1550,19 +3182,51 @@
           <t>Arista Networks</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Arista Networks+careers</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -1571,19 +3235,51 @@
           <t>CrowdStrike</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=CrowdStrike+careers</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -1592,19 +3288,51 @@
           <t>Palo Alto Networks</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Palo Alto Networks+careers</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -1613,19 +3341,51 @@
           <t>Fortinet</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Fortinet+careers</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -1634,19 +3394,51 @@
           <t>Zscaler</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Zscaler+careers</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -1655,19 +3447,51 @@
           <t>Check Point</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Check Point+careers</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -1676,19 +3500,51 @@
           <t>Okta</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Okta+careers</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -1697,19 +3553,51 @@
           <t>Databricks</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Databricks+careers</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -1718,19 +3606,51 @@
           <t>Atlassian</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=Atlassian+careers</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
     </row>
   </sheetData>
